--- a/deliverables/exports/track-a/01-service-offer-matrix.xlsx
+++ b/deliverables/exports/track-a/01-service-offer-matrix.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The six vector table" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.6 Demand driver" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.7 Demand driver variants" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carried forward" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Added from Block 1 research, a" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carried forward" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -623,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -828,7 +829,141 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>Added from Block 1 research, a seventh service item to rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>`00-BUYER-CHECKS.md` validates Track A more strongly than anything else in the run. Track A's clients sell at deal sizes where every gate in that research is real: procurement, legal review and a security questionnaire become normal above roughly $25,000 annual contract value, and above $100,000 the cycle runs 90 to 180 plus days with a reported 35 to 40 percent of elapsed time inside legal and procurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>That surfaces a service item the original list did not have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Scored provisionally at demand 11.2, competitiveness 16.4, which places it in quadrant 1 alongside market entry strategy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>**Why it belongs.** Phase 7 stage 1 already records that Track A's buyer describes the problem as deals stalling after the pitch. The research names exactly where they stall and what clears it: W-8BEN-E accuracy, a security evidence pack in place of SOC 2, insurance certificates, a DPA, and proof assets the client's champion can forward to four departments. That is a scopeable, checkable deliverable, which is rare in this offer set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>**Why it also improves the economics.** Phase 1 found the first two or three engagements are loss-making in hours because buyer research does not transfer across sub-sectors. Vendor onboarding readiness is the exception. The tax forms, the security pack structure, the contract artifacts and the insurance requirements are substantially the same for every client. It is the first genuinely reusable asset in Track A, and it argues for building it before the second engagement rather than after the fifth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>**Before pricing it, settle `00-CONFLICTS-TO-RESOLVE.md` conflict 6.** Whether a client in the five origin markets can obtain insurance a North American buyer accepts is unresearched, and it is part of this deliverable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
           <t>Carried forward</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="53" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Goes to</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Market entry strategy as anchor, training as entry</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Phase 9 engagement design</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Vertical concentration for unit economics</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Phase 4 ICP, Phase 8 partnerships</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Four to six live conversations, capacity ceiling</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Phase 8 channel sizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Cost of the alternative briefing</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Phase 9 anchor 2</t>
         </is>
       </c>
     </row>
@@ -1924,77 +2059,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="53" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Carried forward</t>
+          <t>Added from Block 1 research, a seventh service item to rate</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Output</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Goes to</t>
+          <t>Service item</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Competitiveness</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Delivery effort</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Funnel role</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Market entry strategy as anchor, training as entry</t>
-        </is>
+      <c r="A4" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Phase 9 engagement design</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Vertical concentration for unit economics</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Phase 4 ICP, Phase 8 partnerships</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Four to six live conversations, capacity ceiling</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Phase 8 channel sizing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Cost of the alternative briefing</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Phase 9 anchor 2</t>
+          <t>Vendor onboarding readiness. Getting the client through a North American buyer's procurement, security, legal and finance lanes</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wanted by most, once they have stalled once</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Unique to us</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>High once, then partly reusable across clients in a vertical</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Differentiator, and the most concrete deliverable in the set</t>
         </is>
       </c>
     </row>
